--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
@@ -1,256 +1,230 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E1BFD8-DDC5-4C9C-A945-E39DA07BA3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
-  <si>
-    <t xml:space="preserve">pregnancy_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">person_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_at_start_of_pregnancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_old</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_start_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meaning_start_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_ongoing_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meaning_ongoing_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_end_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meaning_end_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type_of_pregnancy_end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codvar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coding_system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imputed_start_of_pregnancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imputed_end_of_pregnancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meaning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUROCAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONCEPTSETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONCEPTSET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEMSETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coloured_order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_of_records_in_the_group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order_quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">algorithm_for_reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_splitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">survey_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visit_occurrence_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">origin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">child_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">highest_quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_oldest_record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_most_recent_record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distance_from_oldest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">predicted_day_from_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_start_date_predicted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_end_date_predicted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_start_date_green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">days_from_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_principal_record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start_integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestage_at_first_record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOSTFU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40348529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spontaneousabortion_narrow_W82001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imputed_from_Spontaneousabortion_narrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from_Spontaneousabortion_narrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W82001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICPC2P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hospitalisation_primary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spontaneousabortion_narrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2_yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TypeDiff:YY_YY:DiscordantEnd_TypeDiff:YY_YY:DiscordantEnd_YR:Inconsistency_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:Spontaneousabortion_narrow/2:Interruption_possible/3:Spontaneousabortion_possible/4:Ongoingpregnancy/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datos_generales_paciente_Spontaneousabortion_narrow_dummy_visit_occ_id_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datos_generales_paciente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40348529_record_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+  <si>
+    <t>pregnancy_id</t>
+  </si>
+  <si>
+    <t>record_type</t>
+  </si>
+  <si>
+    <t>record_year</t>
+  </si>
+  <si>
+    <t>person_id</t>
+  </si>
+  <si>
+    <t>age_at_start_of_pregnancy</t>
+  </si>
+  <si>
+    <t>n_old</t>
+  </si>
+  <si>
+    <t>record_date</t>
+  </si>
+  <si>
+    <t>pregnancy_start_date</t>
+  </si>
+  <si>
+    <t>meaning_start_date</t>
+  </si>
+  <si>
+    <t>pregnancy_ongoing_date</t>
+  </si>
+  <si>
+    <t>meaning_ongoing_date</t>
+  </si>
+  <si>
+    <t>pregnancy_end_date</t>
+  </si>
+  <si>
+    <t>meaning_end_date</t>
+  </si>
+  <si>
+    <t>type_of_pregnancy_end</t>
+  </si>
+  <si>
+    <t>codvar</t>
+  </si>
+  <si>
+    <t>coding_system</t>
+  </si>
+  <si>
+    <t>imputed_start_of_pregnancy</t>
+  </si>
+  <si>
+    <t>imputed_end_of_pregnancy</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
+    <t>PROMPT</t>
+  </si>
+  <si>
+    <t>EUROCAT</t>
+  </si>
+  <si>
+    <t>CONCEPTSETS</t>
+  </si>
+  <si>
+    <t>CONCEPTSET</t>
+  </si>
+  <si>
+    <t>ITEMSETS</t>
+  </si>
+  <si>
+    <t>coloured_order</t>
+  </si>
+  <si>
+    <t>number_of_records_in_the_group</t>
+  </si>
+  <si>
+    <t>number_green</t>
+  </si>
+  <si>
+    <t>number_yellow</t>
+  </si>
+  <si>
+    <t>number_blue</t>
+  </si>
+  <si>
+    <t>number_red</t>
+  </si>
+  <si>
+    <t>order_quality</t>
+  </si>
+  <si>
+    <t>algorithm_for_reconciliation</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>pregnancy_splitted</t>
+  </si>
+  <si>
+    <t>survey_id</t>
+  </si>
+  <si>
+    <t>visit_occurrence_id</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>child_id</t>
+  </si>
+  <si>
+    <t>highest_quality</t>
+  </si>
+  <si>
+    <t>date_of_oldest_record</t>
+  </si>
+  <si>
+    <t>date_of_most_recent_record</t>
+  </si>
+  <si>
+    <t>record_id</t>
+  </si>
+  <si>
+    <t>distance_from_oldest</t>
+  </si>
+  <si>
+    <t>train_set</t>
+  </si>
+  <si>
+    <t>predicted_day_from_start</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>pregnancy_start_date_predicted</t>
+  </si>
+  <si>
+    <t>pregnancy_end_date_predicted</t>
+  </si>
+  <si>
+    <t>pregnancy_start_date_green</t>
+  </si>
+  <si>
+    <t>days_from_start</t>
+  </si>
+  <si>
+    <t>date_of_principal_record</t>
+  </si>
+  <si>
+    <t>start_integer</t>
+  </si>
+  <si>
+    <t>weighted_start</t>
+  </si>
+  <si>
+    <t>gestage_at_first_record</t>
+  </si>
+  <si>
+    <t>LOSTFU</t>
+  </si>
+  <si>
+    <t>gestage</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>2_yellow</t>
+  </si>
+  <si>
+    <t>datos_generales_paciente_Spontaneousabortion_narrow_dummy_visit_occ_id_24</t>
+  </si>
+  <si>
+    <t>datos_generales_paciente</t>
+  </si>
+  <si>
+    <t>40348529_record_1</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>preg_1</t>
+  </si>
+  <si>
+    <t>person_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -264,12 +238,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -284,14 +264,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -573,11 +573,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BE2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.42578125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+    <col min="15" max="15" width="7.85546875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="27.140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="26.5703125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="22.42578125" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="28" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="32" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="12" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="73.7109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="103.7109375" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="18.28515625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="9.5703125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="76" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="24.7109375" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="8" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="21.5703125" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="18" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="20.5703125" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="24.42578125" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="6" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="4" hidden="1" customWidth="1"/>
+    <col min="48" max="48" width="30.42578125" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="29.85546875" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="26.85546875" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="23.7109375" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="14.5703125" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="7.85546875" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -750,161 +809,104 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4">
+        <v>40294</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="L2" s="4">
+        <v>40364</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="Z2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="AK2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN2" s="3">
         <v>40364</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="AO2" s="3">
+        <v>40372</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV2" s="3">
         <v>40294</v>
       </c>
-      <c r="I2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2"/>
-      <c r="L2" s="1" t="n">
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="3"/>
+      <c r="AZ2" s="3">
         <v>40364</v>
       </c>
-      <c r="M2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="BA2" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BB2" s="3">
+        <v>40302</v>
+      </c>
+      <c r="BC2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O2" t="s">
+      <c r="BD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="P2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U2" t="s">
-        <v>66</v>
-      </c>
-      <c r="V2" t="s">
-        <v>67</v>
-      </c>
-      <c r="W2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL2"/>
-      <c r="AM2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN2" s="1" t="n">
-        <v>40364</v>
-      </c>
-      <c r="AO2" s="1" t="n">
-        <v>40372</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2" t="n">
-        <v>300</v>
-      </c>
-      <c r="AV2" s="1" t="n">
-        <v>40294</v>
-      </c>
-      <c r="AW2" s="1"/>
-      <c r="AX2" s="1"/>
-      <c r="AY2"/>
-      <c r="AZ2" s="1" t="n">
-        <v>40364</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>14725</v>
-      </c>
-      <c r="BB2" s="1" t="n">
-        <v>40302</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E1BFD8-DDC5-4C9C-A945-E39DA07BA3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2251EC-9E02-4A51-8D05-73BF6558E6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="15810" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
   <si>
     <t>pregnancy_id</t>
   </si>
@@ -218,6 +218,27 @@
   </si>
   <si>
     <t>person_1</t>
+  </si>
+  <si>
+    <t>UNK</t>
+  </si>
+  <si>
+    <t>person_3_UNK</t>
+  </si>
+  <si>
+    <t>preg_1_p3_UNK</t>
+  </si>
+  <si>
+    <t>preg_1_p4_UNK</t>
+  </si>
+  <si>
+    <t>person_4_UNK</t>
+  </si>
+  <si>
+    <t>preg_2_p4_UNK</t>
+  </si>
+  <si>
+    <t>preg_2_p3_UNK</t>
   </si>
 </sst>
 </file>
@@ -238,7 +259,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,6 +269,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -264,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -276,6 +309,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -574,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -905,6 +950,418 @@
         <v>63</v>
       </c>
     </row>
+    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8">
+        <v>43885</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8">
+        <v>44165</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>40364</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>40372</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>40294</v>
+      </c>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AZ3" s="3">
+        <v>40364</v>
+      </c>
+      <c r="BA3" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BB3" s="3">
+        <v>40302</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="BD3" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8">
+        <v>40233</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8">
+        <v>40512</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>40364</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>40372</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>40294</v>
+      </c>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AZ4" s="3">
+        <v>40364</v>
+      </c>
+      <c r="BA4" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>40302</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="BD4" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6">
+        <v>43548</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="6">
+        <v>43845</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>40364</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>40372</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV5" s="3">
+        <v>40294</v>
+      </c>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AZ5" s="3">
+        <v>40364</v>
+      </c>
+      <c r="BA5" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BB5" s="3">
+        <v>40302</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="BD5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
+        <v>43885</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6">
+        <v>44165</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>40364</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>40372</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>40294</v>
+      </c>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AZ6" s="3">
+        <v>40364</v>
+      </c>
+      <c r="BA6" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>40302</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2251EC-9E02-4A51-8D05-73BF6558E6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E04CC07-A214-4985-9084-4BB94DB5FCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15810" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11340" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>pregnancy_id</t>
   </si>
@@ -239,13 +239,34 @@
   </si>
   <si>
     <t>preg_2_p3_UNK</t>
+  </si>
+  <si>
+    <t>person_rule3_1</t>
+  </si>
+  <si>
+    <t>person_rule3_2</t>
+  </si>
+  <si>
+    <t>preg_1_person_1_rule3</t>
+  </si>
+  <si>
+    <t>preg_2_person_1_rule3</t>
+  </si>
+  <si>
+    <t>person_1_rule3</t>
+  </si>
+  <si>
+    <t>preg_1_person_2_rule3</t>
+  </si>
+  <si>
+    <t>person_2_rule3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -258,8 +279,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,6 +311,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -297,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -321,6 +354,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -619,69 +659,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE6"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BE9"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.42578125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" customWidth="1"/>
-    <col min="15" max="15" width="7.85546875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="27.140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="26.5703125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="22.42578125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.44140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.44140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="27.109375" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="26.5546875" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="22.44140625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.44140625" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="28" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="14.88671875" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="32" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="13.109375" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="12" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="73.7109375" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="103.7109375" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="18.28515625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="9.5703125" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="73.6640625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="103.6640625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="18.33203125" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="9.5546875" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="76" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="24.7109375" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="24.6640625" hidden="1" customWidth="1"/>
     <col min="38" max="38" width="8" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="21.5703125" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="21.5546875" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="27.33203125" hidden="1" customWidth="1"/>
     <col min="42" max="42" width="18" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.5703125" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="8.85546875" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="24.42578125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="20.5546875" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="24.44140625" hidden="1" customWidth="1"/>
     <col min="46" max="46" width="6" hidden="1" customWidth="1"/>
     <col min="47" max="47" width="4" hidden="1" customWidth="1"/>
-    <col min="48" max="48" width="30.42578125" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="29.85546875" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="26.85546875" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="23.7109375" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="14.5703125" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="7.5703125" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="7.85546875" hidden="1" customWidth="1"/>
+    <col min="48" max="48" width="30.44140625" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="29.88671875" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="26.88671875" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="15.44140625" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="23.6640625" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="14.5546875" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="22.33203125" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="7.5546875" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="7.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -854,7 +894,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>64</v>
       </c>
@@ -950,7 +990,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>68</v>
       </c>
@@ -1053,7 +1093,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>72</v>
       </c>
@@ -1156,7 +1196,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>69</v>
       </c>
@@ -1259,7 +1299,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>71</v>
       </c>
@@ -1362,7 +1402,98 @@
         <v>63</v>
       </c>
     </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10">
+        <v>43466</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="10">
+        <v>43709</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10">
+        <v>43831</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="10">
+        <v>44075</v>
+      </c>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10">
+        <v>43466</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="10">
+        <v>43709</v>
+      </c>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_pregnancy_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E04CC07-A214-4985-9084-4BB94DB5FCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0234A658-E25A-4EF6-B973-E04EF2E2BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11340" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
   <si>
     <t>pregnancy_id</t>
   </si>
@@ -260,6 +260,24 @@
   </si>
   <si>
     <t>person_2_rule3</t>
+  </si>
+  <si>
+    <t>preg_1_person_1_rule5</t>
+  </si>
+  <si>
+    <t>person_1_rule5</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>preg_1_person_2_rule5</t>
+  </si>
+  <si>
+    <t>preg_2_person_2_rule5</t>
+  </si>
+  <si>
+    <t>person_2_rule5</t>
   </si>
 </sst>
 </file>
@@ -286,7 +304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +335,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -330,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -361,6 +385,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -659,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE9"/>
+  <dimension ref="A1:BE12"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -1492,6 +1523,96 @@
         <v>66</v>
       </c>
     </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13">
+        <v>43709</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="13">
+        <v>43983</v>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13">
+        <v>43709</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="13">
+        <v>43983</v>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13">
+        <v>43344</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="13">
+        <v>43617</v>
+      </c>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
